--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/OREGON_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/OREGON_2015.xlsx
@@ -1327,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="55">
@@ -3901,7 +3901,7 @@
         <v>15</v>
       </c>
       <c r="D197">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="198">
@@ -4279,7 +4279,7 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="219">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C241">
@@ -5377,7 +5377,7 @@
         <v>15</v>
       </c>
       <c r="D279">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="280">
@@ -5503,7 +5503,7 @@
         <v>15</v>
       </c>
       <c r="D286">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="287">
@@ -6097,7 +6097,7 @@
         <v>15</v>
       </c>
       <c r="D319">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="320">
@@ -6187,7 +6187,7 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="325">
@@ -6457,7 +6457,7 @@
         <v>15</v>
       </c>
       <c r="D339">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="340">
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="D367">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="368">
@@ -9895,7 +9895,7 @@
         <v>15</v>
       </c>
       <c r="D530">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="531">
@@ -11227,7 +11227,7 @@
         <v>15</v>
       </c>
       <c r="D604">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="605">
@@ -12217,7 +12217,7 @@
         <v>15</v>
       </c>
       <c r="D659">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="660">
@@ -12379,7 +12379,7 @@
         <v>15</v>
       </c>
       <c r="D668">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="669">
@@ -12451,7 +12451,7 @@
         <v>15</v>
       </c>
       <c r="D672">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="673">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C770">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C771">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C816">
@@ -15079,7 +15079,7 @@
         <v>15</v>
       </c>
       <c r="D818">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="819">
@@ -16645,7 +16645,7 @@
         <v>15</v>
       </c>
       <c r="D905">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="906">
@@ -17419,7 +17419,7 @@
         <v>15</v>
       </c>
       <c r="D948">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="949">
@@ -18085,7 +18085,7 @@
         <v>15</v>
       </c>
       <c r="D985">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="986">
@@ -20353,7 +20353,7 @@
         <v>15</v>
       </c>
       <c r="D1111">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="1112">
@@ -21343,7 +21343,7 @@
         <v>15</v>
       </c>
       <c r="D1166">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="1167">
@@ -23539,7 +23539,7 @@
         <v>15</v>
       </c>
       <c r="D1288">
-        <v>0.0009447628645210053</v>
+        <v>0.0009447628645210052</v>
       </c>
     </row>
     <row r="1289">
